--- a/results.xlsx
+++ b/results.xlsx
@@ -8,20 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b3b8483b84de6896/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="153" documentId="8_{145C42C3-443D-4E15-93B8-1F2CB8F007B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6DCBDA20-3C08-4964-A9B1-5358321EE030}"/>
+  <xr:revisionPtr revIDLastSave="331" documentId="8_{145C42C3-443D-4E15-93B8-1F2CB8F007B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A7500FE4-0792-48A4-8F29-6C3C0C4B145D}"/>
   <bookViews>
-    <workbookView xWindow="-1590" yWindow="2400" windowWidth="16680" windowHeight="10260" xr2:uid="{24CE1277-A613-4720-ADC8-033736813124}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{24CE1277-A613-4720-ADC8-033736813124}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="6" r:id="rId1"/>
-    <sheet name="男子部 2026" sheetId="1" r:id="rId2"/>
-    <sheet name="女子部 2026" sheetId="2" r:id="rId3"/>
-    <sheet name="看護部 2026" sheetId="5" r:id="rId4"/>
+    <sheet name="MENS2026" sheetId="1" r:id="rId2"/>
+    <sheet name="WOMENS2026" sheetId="2" r:id="rId3"/>
+    <sheet name="NURSING2026" sheetId="5" r:id="rId4"/>
+    <sheet name="OBOG2026" sheetId="7" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'看護部 2026'!$A$1:$M$24</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'女子部 2026'!$A$1:$M$41</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'男子部 2026'!$A$1:$M$54</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">MENS2026!$A$1:$M$54</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">NURSING2026!$A$1:$M$24</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">WOMENS2026!$A$1:$M$41</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -47,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="648" uniqueCount="309">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="727" uniqueCount="340">
   <si>
     <t>横浜市立大学</t>
   </si>
@@ -905,18 +906,6 @@
     <phoneticPr fontId="5"/>
   </si>
   <si>
-    <t>Opponent</t>
-    <phoneticPr fontId="5"/>
-  </si>
-  <si>
-    <t>YCU</t>
-    <phoneticPr fontId="5"/>
-  </si>
-  <si>
-    <t>Opp</t>
-    <phoneticPr fontId="5"/>
-  </si>
-  <si>
     <t>Result</t>
     <phoneticPr fontId="5"/>
   </si>
@@ -973,13 +962,6 @@
     <phoneticPr fontId="5"/>
   </si>
   <si>
-    <t>東医体</t>
-    <rPh sb="0" eb="3">
-      <t>トウイタイ</t>
-    </rPh>
-    <phoneticPr fontId="5"/>
-  </si>
-  <si>
     <t>1回戦</t>
     <rPh sb="1" eb="3">
       <t>カイセン</t>
@@ -1088,13 +1070,184 @@
   </si>
   <si>
     <t>N2026-04</t>
+  </si>
+  <si>
+    <t>OBOG</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>https://youtu.be/ELCgjPq0wVA</t>
+  </si>
+  <si>
+    <t>1-3</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>2-2</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>Home score</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>Away Score</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>Away</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>Home</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>西田・才田</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>三宅・都竹</t>
+    <rPh sb="0" eb="2">
+      <t>ミヤケ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>トタケ</t>
+    </rPh>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>三谷・阿部</t>
+    <rPh sb="0" eb="2">
+      <t>ミタニ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>アベ</t>
+    </rPh>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>https://youtu.be/nybQkEeNGKY</t>
+  </si>
+  <si>
+    <t>3番コート</t>
+    <rPh sb="1" eb="2">
+      <t>バン</t>
+    </rPh>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Home </t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>2番コート</t>
+    <rPh sb="1" eb="2">
+      <t>バン</t>
+    </rPh>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>1番コート</t>
+    <rPh sb="1" eb="2">
+      <t>バン</t>
+    </rPh>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>1試合目</t>
+    <rPh sb="1" eb="4">
+      <t>シアイメ</t>
+    </rPh>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>2試合目</t>
+    <rPh sb="1" eb="4">
+      <t>シアイメ</t>
+    </rPh>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>3試合目</t>
+    <rPh sb="1" eb="4">
+      <t>シアイメ</t>
+    </rPh>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>4試合目</t>
+    <rPh sb="1" eb="4">
+      <t>シアイメ</t>
+    </rPh>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>西田・才田</t>
+    <rPh sb="0" eb="2">
+      <t>ニシダ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>サイタ</t>
+    </rPh>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>2-4</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>OB2026-01-03</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>OB2026-02-02</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>MATCHID</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>https://youtu.be/f0lRhsN8p0U</t>
+  </si>
+  <si>
+    <t>https://youtu.be/fGQRI6VjNjQ</t>
+  </si>
+  <si>
+    <t>https://youtu.be/pE1wsB_KxDc</t>
+  </si>
+  <si>
+    <t>https://youtu.be/1IoP-l3guIg</t>
+  </si>
+  <si>
+    <t>https://youtu.be/KkUtSax6r5g</t>
+  </si>
+  <si>
+    <t>https://youtube.com/playlist?list=PLLElW6C9F9M4&amp;si=r1xZe4azBnVIs7iy</t>
+  </si>
+  <si>
+    <t>MEN</t>
+  </si>
+  <si>
+    <t>WOMEN</t>
+  </si>
+  <si>
+    <t>Toitai</t>
+  </si>
+  <si>
+    <t>横浜市立大学</t>
+    <rPh sb="0" eb="6">
+      <t>ヨコハマシリツダイガク</t>
+    </rPh>
+    <phoneticPr fontId="5"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1154,13 +1307,19 @@
       <charset val="128"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ 明朝"/>
+      <family val="1"/>
+      <charset val="128"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
-      <family val="3"/>
+      <name val="ＭＳ 明朝"/>
+      <family val="1"/>
       <charset val="128"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -1177,7 +1336,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -1226,13 +1385,93 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1260,8 +1499,41 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1273,12 +1545,18 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1293,20 +1571,14 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1646,613 +1918,770 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03952BFE-52BA-4D7B-8D77-B58F5D0C9EF4}">
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:K20"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.6640625" style="23"/>
-    <col min="3" max="3" width="15.33203125" style="23" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="8.6640625" style="23"/>
-    <col min="6" max="6" width="18.25" style="23" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.75" style="23" customWidth="1"/>
-    <col min="8" max="8" width="9.25" style="23" customWidth="1"/>
-    <col min="9" max="9" width="8.6640625" style="23"/>
-    <col min="10" max="10" width="34.9140625" customWidth="1"/>
+    <col min="1" max="1" width="14.25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.08203125" customWidth="1"/>
+    <col min="5" max="5" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.83203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.25" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.75" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="34.9140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" t="s">
-        <v>291</v>
-      </c>
-      <c r="B1" s="22" t="s">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="17" t="s">
+        <v>287</v>
+      </c>
+      <c r="B1" s="17" t="s">
         <v>265</v>
       </c>
-      <c r="C1" s="22" t="s">
+      <c r="C1" s="17" t="s">
         <v>266</v>
       </c>
-      <c r="D1" s="22" t="s">
+      <c r="D1" s="17" t="s">
         <v>267</v>
       </c>
-      <c r="E1" s="22" t="s">
+      <c r="E1" s="17" t="s">
         <v>268</v>
       </c>
-      <c r="F1" s="22" t="s">
+      <c r="F1" s="17" t="s">
+        <v>312</v>
+      </c>
+      <c r="G1" s="17" t="s">
+        <v>311</v>
+      </c>
+      <c r="H1" s="17" t="s">
+        <v>309</v>
+      </c>
+      <c r="I1" s="17" t="s">
+        <v>310</v>
+      </c>
+      <c r="J1" s="17" t="s">
         <v>269</v>
       </c>
-      <c r="G1" s="22" t="s">
+      <c r="K1" s="18" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="10" t="s">
+        <v>288</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>336</v>
+      </c>
+      <c r="C2" s="19">
+        <v>46159</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>271</v>
+      </c>
+      <c r="E2" s="10" t="s">
+        <v>272</v>
+      </c>
+      <c r="F2" s="10" t="s">
+        <v>339</v>
+      </c>
+      <c r="G2" s="10" t="str">
+        <f>MENS2026!$F$3</f>
+        <v>東京科学大学</v>
+      </c>
+      <c r="H2" s="10">
+        <f>MENS2026!$D$4</f>
+        <v>3</v>
+      </c>
+      <c r="I2" s="10">
+        <f>MENS2026!$F$4</f>
+        <v>6</v>
+      </c>
+      <c r="J2" s="10" t="str">
+        <f>IF(H2&gt;I2,"WIN",IF(H2&lt;I2,"LOSS",""))</f>
+        <v>LOSS</v>
+      </c>
+      <c r="K2" s="10" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="10" t="s">
+        <v>289</v>
+      </c>
+      <c r="B3" s="10" t="s">
         <v>270</v>
       </c>
-      <c r="H1" s="22" t="s">
+      <c r="C3" s="19">
+        <v>46173</v>
+      </c>
+      <c r="D3" s="10" t="s">
         <v>271</v>
       </c>
-      <c r="I1" s="22" t="s">
-        <v>272</v>
-      </c>
-      <c r="J1" s="9" t="s">
+      <c r="E3" s="10" t="s">
+        <v>273</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>339</v>
+      </c>
+      <c r="G3" s="10" t="str">
+        <f>MENS2026!$L$3</f>
+        <v>東京慈恵会医科大学</v>
+      </c>
+      <c r="H3" s="10">
+        <f>MENS2026!$J$4</f>
+        <v>6</v>
+      </c>
+      <c r="I3" s="10">
+        <f>MENS2026!$L$4</f>
+        <v>3</v>
+      </c>
+      <c r="J3" s="10" t="str">
+        <f t="shared" ref="J3:J16" si="0">IF(H3&gt;I3,"WIN",IF(H3&lt;I3,"LOSS",""))</f>
+        <v>WIN</v>
+      </c>
+      <c r="K3" s="10" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" s="10" t="s">
         <v>290</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" t="s">
-        <v>292</v>
-      </c>
-      <c r="B2" s="23" t="s">
-        <v>273</v>
-      </c>
-      <c r="C2" s="24">
-        <v>46159</v>
-      </c>
-      <c r="D2" s="23" t="s">
+      <c r="B4" s="10" t="s">
+        <v>270</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>276</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>271</v>
+      </c>
+      <c r="E4" s="10" t="s">
         <v>274</v>
       </c>
-      <c r="E2" s="23" t="s">
-        <v>275</v>
-      </c>
-      <c r="F2" s="23" t="str">
-        <f>'男子部 2026'!$F$3</f>
-        <v>東京科学大学</v>
-      </c>
-      <c r="G2" s="23">
-        <f>'男子部 2026'!$D$4</f>
+      <c r="F4" s="10" t="s">
+        <v>339</v>
+      </c>
+      <c r="G4" s="10" t="str">
+        <f>MENS2026!$F$17</f>
+        <v>東京大学</v>
+      </c>
+      <c r="H4" s="10">
+        <f>MENS2026!$D$18</f>
         <v>3</v>
       </c>
-      <c r="H2" s="23">
-        <f>'男子部 2026'!$F$4</f>
-        <v>6</v>
-      </c>
-      <c r="I2" s="23" t="str">
-        <f>IF(G2&gt;H2,"WIN",IF(G2&lt;H2,"LOSS",""))</f>
-        <v>LOSS</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" t="s">
-        <v>293</v>
-      </c>
-      <c r="B3" s="23" t="s">
-        <v>273</v>
-      </c>
-      <c r="C3" s="24">
-        <v>46173</v>
-      </c>
-      <c r="D3" s="23" t="s">
-        <v>274</v>
-      </c>
-      <c r="E3" s="23" t="s">
-        <v>276</v>
-      </c>
-      <c r="F3" s="23" t="str">
-        <f>'男子部 2026'!$L$3</f>
-        <v>東京慈恵会医科大学</v>
-      </c>
-      <c r="G3" s="23">
-        <f>'男子部 2026'!$J$4</f>
-        <v>6</v>
-      </c>
-      <c r="H3" s="23">
-        <f>'男子部 2026'!$L$4</f>
-        <v>3</v>
-      </c>
-      <c r="I3" s="23" t="str">
-        <f t="shared" ref="I3:I16" si="0">IF(G3&gt;H3,"WIN",IF(G3&lt;H3,"LOSS",""))</f>
-        <v>WIN</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" t="s">
-        <v>294</v>
-      </c>
-      <c r="B4" s="23" t="s">
-        <v>273</v>
-      </c>
-      <c r="C4" s="23" t="s">
-        <v>279</v>
-      </c>
-      <c r="D4" s="23" t="s">
-        <v>274</v>
-      </c>
-      <c r="E4" s="23" t="s">
-        <v>277</v>
-      </c>
-      <c r="F4" s="23" t="str">
-        <f>'男子部 2026'!$F$17</f>
-        <v>東京大学</v>
-      </c>
-      <c r="G4" s="23">
-        <f>'男子部 2026'!$D$18</f>
-        <v>3</v>
-      </c>
-      <c r="H4" s="23">
-        <f>'男子部 2026'!$F$18</f>
+      <c r="I4" s="10">
+        <f>MENS2026!$F$18</f>
         <v>5</v>
       </c>
-      <c r="I4" s="23" t="str">
+      <c r="J4" s="10" t="str">
         <f t="shared" si="0"/>
         <v>LOSS</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" t="s">
-        <v>295</v>
-      </c>
-      <c r="B5" s="23" t="s">
-        <v>273</v>
-      </c>
-      <c r="C5" s="24">
+      <c r="K4" s="10" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="10" t="s">
+        <v>291</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>270</v>
+      </c>
+      <c r="C5" s="19">
         <v>46215</v>
       </c>
-      <c r="D5" s="23" t="s">
-        <v>274</v>
-      </c>
-      <c r="E5" s="23" t="s">
-        <v>278</v>
-      </c>
-      <c r="F5" s="23" t="s">
+      <c r="D5" s="10" t="s">
+        <v>271</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>275</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>339</v>
+      </c>
+      <c r="G5" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="G5" s="23">
-        <f>'男子部 2026'!$J$18</f>
+      <c r="H5" s="10">
+        <f>MENS2026!$J$18</f>
         <v>4</v>
       </c>
-      <c r="H5" s="23">
-        <f>'男子部 2026'!$L$18</f>
+      <c r="I5" s="10">
+        <f>MENS2026!$L$18</f>
         <v>5</v>
       </c>
-      <c r="I5" s="23" t="str">
+      <c r="J5" s="10" t="str">
         <f t="shared" si="0"/>
         <v>LOSS</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" t="s">
-        <v>296</v>
-      </c>
-      <c r="B6" s="23" t="s">
-        <v>273</v>
-      </c>
-      <c r="C6" s="24">
+      <c r="K5" s="10" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="10" t="s">
+        <v>292</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>270</v>
+      </c>
+      <c r="C6" s="19">
         <v>46235</v>
       </c>
-      <c r="D6" s="23" t="s">
-        <v>280</v>
-      </c>
-      <c r="E6" s="23" t="s">
-        <v>281</v>
-      </c>
-      <c r="F6" s="23" t="str">
-        <f>'男子部 2026'!$F$31</f>
+      <c r="D6" s="10" t="s">
+        <v>338</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>277</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>339</v>
+      </c>
+      <c r="G6" s="10" t="str">
+        <f>MENS2026!$F$31</f>
         <v>東海大学</v>
       </c>
-      <c r="G6" s="23">
-        <f>'男子部 2026'!$D$32</f>
+      <c r="H6" s="10">
+        <f>MENS2026!$D$32</f>
         <v>4</v>
       </c>
-      <c r="H6" s="23">
-        <f>'男子部 2026'!$F$32</f>
+      <c r="I6" s="10">
+        <f>MENS2026!$F$32</f>
         <v>1</v>
       </c>
-      <c r="I6" s="23" t="str">
+      <c r="J6" s="10" t="str">
         <f t="shared" si="0"/>
         <v>WIN</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" t="s">
-        <v>297</v>
-      </c>
-      <c r="B7" s="23" t="s">
-        <v>273</v>
-      </c>
-      <c r="C7" s="24">
+      <c r="K6" s="10" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="10" t="s">
+        <v>293</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>270</v>
+      </c>
+      <c r="C7" s="19">
         <v>46236</v>
       </c>
-      <c r="D7" s="23" t="s">
-        <v>280</v>
-      </c>
-      <c r="E7" s="23" t="s">
-        <v>282</v>
-      </c>
-      <c r="F7" s="23" t="str">
-        <f>'男子部 2026'!$L$31</f>
+      <c r="D7" s="10" t="s">
+        <v>338</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>278</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>339</v>
+      </c>
+      <c r="G7" s="10" t="str">
+        <f>MENS2026!$L$31</f>
         <v>防衛医科大学</v>
       </c>
-      <c r="G7" s="23">
-        <f>'男子部 2026'!$J$32</f>
+      <c r="H7" s="10">
+        <f>MENS2026!$J$32</f>
         <v>2</v>
       </c>
-      <c r="H7" s="23">
-        <f>'男子部 2026'!$L$32</f>
+      <c r="I7" s="10">
+        <f>MENS2026!$L$32</f>
         <v>3</v>
       </c>
-      <c r="I7" s="23" t="str">
+      <c r="J7" s="10" t="str">
         <f t="shared" si="0"/>
         <v>LOSS</v>
       </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" t="s">
-        <v>298</v>
-      </c>
-      <c r="B8" s="23" t="s">
-        <v>283</v>
-      </c>
-      <c r="C8" s="24">
+      <c r="K7" s="10" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="10" t="s">
+        <v>294</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>337</v>
+      </c>
+      <c r="C8" s="19">
         <v>46152</v>
       </c>
-      <c r="D8" s="23" t="s">
-        <v>274</v>
-      </c>
-      <c r="E8" s="23" t="s">
-        <v>275</v>
-      </c>
-      <c r="F8" s="23" t="str">
-        <f>'女子部 2026'!$F$3</f>
+      <c r="D8" s="10" t="s">
+        <v>271</v>
+      </c>
+      <c r="E8" s="10" t="s">
+        <v>272</v>
+      </c>
+      <c r="F8" s="10" t="s">
+        <v>339</v>
+      </c>
+      <c r="G8" s="10" t="str">
+        <f>WOMENS2026!$F$3</f>
         <v>日本大学</v>
       </c>
-      <c r="G8" s="23">
-        <f>'女子部 2026'!$D$4</f>
+      <c r="H8" s="10">
+        <f>WOMENS2026!$D$4</f>
         <v>1</v>
       </c>
-      <c r="H8" s="23">
-        <f>'女子部 2026'!$F$4</f>
+      <c r="I8" s="10">
+        <f>WOMENS2026!$F$4</f>
         <v>4</v>
       </c>
-      <c r="I8" s="23" t="str">
+      <c r="J8" s="10" t="str">
         <f t="shared" si="0"/>
         <v>LOSS</v>
       </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" t="s">
-        <v>300</v>
-      </c>
-      <c r="B9" s="23" t="s">
-        <v>283</v>
-      </c>
-      <c r="C9" s="24">
+      <c r="K8" s="10"/>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" s="10" t="s">
+        <v>296</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>279</v>
+      </c>
+      <c r="C9" s="19">
         <v>46159</v>
       </c>
-      <c r="D9" s="23" t="s">
-        <v>274</v>
-      </c>
-      <c r="E9" s="23" t="s">
-        <v>276</v>
-      </c>
-      <c r="F9" s="23" t="str">
-        <f>'女子部 2026'!$L$3</f>
+      <c r="D9" s="10" t="s">
+        <v>271</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>273</v>
+      </c>
+      <c r="F9" s="10" t="s">
+        <v>339</v>
+      </c>
+      <c r="G9" s="10" t="str">
+        <f>WOMENS2026!$L$3</f>
         <v>慶應義塾大学</v>
       </c>
-      <c r="G9" s="23">
-        <f>'女子部 2026'!$J$4</f>
+      <c r="H9" s="10">
+        <f>WOMENS2026!$J$4</f>
         <v>0</v>
       </c>
-      <c r="H9" s="23">
-        <f>'女子部 2026'!$L$4</f>
+      <c r="I9" s="10">
+        <f>WOMENS2026!$L$4</f>
         <v>5</v>
       </c>
-      <c r="I9" s="23" t="str">
+      <c r="J9" s="10" t="str">
         <f t="shared" si="0"/>
         <v>LOSS</v>
       </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" t="s">
-        <v>299</v>
-      </c>
-      <c r="B10" s="23" t="s">
-        <v>283</v>
-      </c>
-      <c r="C10" s="24">
+      <c r="K9" s="10"/>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" s="10" t="s">
+        <v>295</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>279</v>
+      </c>
+      <c r="C10" s="19">
         <v>46173</v>
       </c>
-      <c r="D10" s="23" t="s">
+      <c r="D10" s="10" t="s">
+        <v>271</v>
+      </c>
+      <c r="E10" s="10" t="s">
         <v>274</v>
       </c>
-      <c r="E10" s="23" t="s">
-        <v>277</v>
-      </c>
-      <c r="F10" s="23" t="str">
-        <f>'女子部 2026'!$F$13</f>
+      <c r="F10" s="10" t="s">
+        <v>339</v>
+      </c>
+      <c r="G10" s="10" t="str">
+        <f>WOMENS2026!$F$13</f>
         <v>日本医科大学</v>
       </c>
-      <c r="G10" s="23">
-        <f>'女子部 2026'!$D$14</f>
+      <c r="H10" s="10">
+        <f>WOMENS2026!$D$14</f>
         <v>3</v>
       </c>
-      <c r="H10" s="23">
-        <f>'女子部 2026'!$F$14</f>
+      <c r="I10" s="10">
+        <f>WOMENS2026!$F$14</f>
         <v>2</v>
       </c>
-      <c r="I10" s="23" t="str">
+      <c r="J10" s="10" t="str">
         <f t="shared" si="0"/>
         <v>WIN</v>
       </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" t="s">
-        <v>301</v>
-      </c>
-      <c r="B11" s="23" t="s">
-        <v>283</v>
-      </c>
-      <c r="C11" s="24">
+      <c r="K10" s="10"/>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" s="10" t="s">
+        <v>297</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>279</v>
+      </c>
+      <c r="C11" s="19">
         <v>46180</v>
       </c>
-      <c r="D11" s="23" t="s">
-        <v>274</v>
-      </c>
-      <c r="E11" s="23" t="s">
-        <v>278</v>
-      </c>
-      <c r="F11" s="23" t="str">
-        <f>'女子部 2026'!$L$13</f>
+      <c r="D11" s="10" t="s">
+        <v>271</v>
+      </c>
+      <c r="E11" s="10" t="s">
+        <v>275</v>
+      </c>
+      <c r="F11" s="10" t="s">
+        <v>339</v>
+      </c>
+      <c r="G11" s="10" t="str">
+        <f>WOMENS2026!$L$13</f>
         <v>東京科学大学</v>
       </c>
-      <c r="G11" s="23">
-        <f>'女子部 2026'!$J$14</f>
+      <c r="H11" s="10">
+        <f>WOMENS2026!$J$14</f>
         <v>0</v>
       </c>
-      <c r="H11" s="23">
-        <f>'女子部 2026'!$L$14</f>
+      <c r="I11" s="10">
+        <f>WOMENS2026!$L$14</f>
         <v>0</v>
       </c>
-      <c r="I11" s="23" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" t="s">
-        <v>302</v>
-      </c>
-      <c r="B12" s="23" t="s">
-        <v>283</v>
-      </c>
-      <c r="C12" s="24">
+      <c r="J11" s="10" t="s">
+        <v>280</v>
+      </c>
+      <c r="K11" s="10"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" s="10" t="s">
+        <v>298</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>279</v>
+      </c>
+      <c r="C12" s="19">
         <v>46236</v>
       </c>
-      <c r="D12" s="23" t="s">
-        <v>280</v>
-      </c>
-      <c r="E12" s="23" t="s">
-        <v>281</v>
-      </c>
-      <c r="F12" s="23" t="str">
-        <f>'女子部 2026'!$F$23</f>
+      <c r="D12" s="10" t="s">
+        <v>338</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>277</v>
+      </c>
+      <c r="F12" s="10" t="s">
+        <v>339</v>
+      </c>
+      <c r="G12" s="10" t="str">
+        <f>WOMENS2026!$F$23</f>
         <v>東京医科大学</v>
       </c>
-      <c r="G12" s="23">
-        <f>'女子部 2026'!$D$24</f>
+      <c r="H12" s="10">
+        <f>WOMENS2026!$D$24</f>
         <v>2</v>
       </c>
-      <c r="H12" s="23">
-        <f>'女子部 2026'!$F$24</f>
+      <c r="I12" s="10">
+        <f>WOMENS2026!$F$24</f>
         <v>1</v>
       </c>
-      <c r="I12" s="23" t="str">
+      <c r="J12" s="10" t="str">
         <f t="shared" si="0"/>
         <v>WIN</v>
       </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" t="s">
-        <v>303</v>
-      </c>
-      <c r="B13" s="23" t="s">
-        <v>283</v>
-      </c>
-      <c r="C13" s="24">
+      <c r="K12" s="10"/>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" s="10" t="s">
+        <v>299</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>279</v>
+      </c>
+      <c r="C13" s="19">
         <v>46237</v>
       </c>
-      <c r="D13" s="23" t="s">
-        <v>280</v>
-      </c>
-      <c r="E13" s="23" t="s">
-        <v>282</v>
-      </c>
-      <c r="F13" s="23" t="str">
-        <f>'女子部 2026'!$L$23</f>
+      <c r="D13" s="10" t="s">
+        <v>338</v>
+      </c>
+      <c r="E13" s="10" t="s">
+        <v>278</v>
+      </c>
+      <c r="F13" s="10" t="s">
+        <v>339</v>
+      </c>
+      <c r="G13" s="10" t="str">
+        <f>WOMENS2026!$L$23</f>
         <v>東京慈恵会医科大学</v>
       </c>
-      <c r="G13" s="23">
-        <f>'女子部 2026'!$J$24</f>
+      <c r="H13" s="10">
+        <f>WOMENS2026!$J$24</f>
         <v>2</v>
       </c>
-      <c r="H13" s="23">
-        <f>'女子部 2026'!$L$24</f>
+      <c r="I13" s="10">
+        <f>WOMENS2026!$L$24</f>
         <v>1</v>
       </c>
-      <c r="I13" s="23" t="str">
+      <c r="J13" s="10" t="str">
         <f t="shared" si="0"/>
         <v>WIN</v>
       </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" t="s">
-        <v>304</v>
-      </c>
-      <c r="B14" s="23" t="s">
-        <v>283</v>
-      </c>
-      <c r="C14" s="24">
+      <c r="K13" s="10"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" s="10" t="s">
+        <v>300</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>279</v>
+      </c>
+      <c r="C14" s="19">
         <v>46238</v>
       </c>
-      <c r="D14" s="23" t="s">
-        <v>280</v>
-      </c>
-      <c r="E14" s="23" t="s">
-        <v>286</v>
-      </c>
-      <c r="F14" s="23" t="str">
-        <f>'女子部 2026'!$F$31</f>
+      <c r="D14" s="10" t="s">
+        <v>338</v>
+      </c>
+      <c r="E14" s="10" t="s">
+        <v>282</v>
+      </c>
+      <c r="F14" s="10" t="s">
+        <v>339</v>
+      </c>
+      <c r="G14" s="10" t="str">
+        <f>WOMENS2026!$F$31</f>
         <v>福島県立医科大学</v>
       </c>
-      <c r="G14" s="23">
-        <f>'女子部 2026'!$D$32</f>
+      <c r="H14" s="10">
+        <f>WOMENS2026!$D$32</f>
         <v>0</v>
       </c>
-      <c r="H14" s="23">
-        <f>'女子部 2026'!$F$32</f>
+      <c r="I14" s="10">
+        <f>WOMENS2026!$F$32</f>
         <v>3</v>
       </c>
-      <c r="I14" s="23" t="str">
+      <c r="J14" s="10" t="str">
         <f t="shared" si="0"/>
         <v>LOSS</v>
       </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" t="s">
-        <v>305</v>
-      </c>
-      <c r="B15" s="23" t="s">
-        <v>287</v>
-      </c>
-      <c r="C15" s="24">
+      <c r="K14" s="10"/>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" s="10" t="s">
+        <v>301</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>283</v>
+      </c>
+      <c r="C15" s="19">
         <v>46249</v>
       </c>
-      <c r="D15" s="23" t="s">
-        <v>274</v>
-      </c>
-      <c r="E15" s="23" t="s">
-        <v>275</v>
-      </c>
-      <c r="F15" s="23" t="str">
-        <f>'看護部 2026'!$F$3</f>
+      <c r="D15" s="10" t="s">
+        <v>271</v>
+      </c>
+      <c r="E15" s="10" t="s">
+        <v>272</v>
+      </c>
+      <c r="F15" s="10" t="s">
+        <v>339</v>
+      </c>
+      <c r="G15" s="10" t="str">
+        <f>NURSING2026!$F$3</f>
         <v>山梨大学</v>
       </c>
-      <c r="G15" s="23">
-        <f>'看護部 2026'!$D$4</f>
+      <c r="H15" s="10">
+        <f>NURSING2026!$D$4</f>
         <v>4</v>
       </c>
-      <c r="H15" s="23">
-        <f>'看護部 2026'!$F$4</f>
+      <c r="I15" s="10">
+        <f>NURSING2026!$F$4</f>
         <v>1</v>
       </c>
-      <c r="I15" s="23" t="str">
+      <c r="J15" s="10" t="str">
         <f t="shared" si="0"/>
         <v>WIN</v>
       </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" t="s">
-        <v>306</v>
-      </c>
-      <c r="B16" s="23" t="s">
-        <v>287</v>
-      </c>
-      <c r="C16" s="24">
+      <c r="K15" s="10"/>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" s="10" t="s">
+        <v>302</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>283</v>
+      </c>
+      <c r="C16" s="19">
         <v>46250</v>
       </c>
-      <c r="D16" s="23" t="s">
-        <v>274</v>
-      </c>
-      <c r="E16" s="23" t="s">
-        <v>276</v>
-      </c>
-      <c r="F16" s="23" t="str">
-        <f>'看護部 2026'!$L$3</f>
+      <c r="D16" s="10" t="s">
+        <v>271</v>
+      </c>
+      <c r="E16" s="10" t="s">
+        <v>273</v>
+      </c>
+      <c r="F16" s="10" t="s">
+        <v>339</v>
+      </c>
+      <c r="G16" s="10" t="str">
+        <f>NURSING2026!$L$3</f>
         <v>東京科学大学</v>
       </c>
-      <c r="G16" s="23">
-        <f>'看護部 2026'!$J$4</f>
+      <c r="H16" s="10">
+        <f>NURSING2026!$J$4</f>
         <v>3</v>
       </c>
-      <c r="H16" s="23">
-        <f>'看護部 2026'!$L$4</f>
+      <c r="I16" s="10">
+        <f>NURSING2026!$L$4</f>
         <v>1</v>
       </c>
-      <c r="I16" s="23" t="str">
+      <c r="J16" s="10" t="str">
         <f t="shared" si="0"/>
         <v>WIN</v>
       </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" t="s">
+      <c r="K16" s="10"/>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" s="10" t="s">
+        <v>303</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>283</v>
+      </c>
+      <c r="C17" s="19">
+        <v>46251</v>
+      </c>
+      <c r="D17" s="10" t="s">
+        <v>271</v>
+      </c>
+      <c r="E17" s="10" t="s">
+        <v>284</v>
+      </c>
+      <c r="F17" s="10" t="s">
+        <v>339</v>
+      </c>
+      <c r="G17" s="10" t="str">
+        <f>NURSING2026!$F$13</f>
+        <v>山梨大学</v>
+      </c>
+      <c r="H17" s="10">
+        <f>NURSING2026!$D$14</f>
+        <v>3</v>
+      </c>
+      <c r="I17" s="10">
+        <f>NURSING2026!$F$14</f>
+        <v>0</v>
+      </c>
+      <c r="J17" s="10" t="str">
+        <f>IF(H17&gt;I17,"WIN",IF(H17&lt;I17,"LOSS",""))</f>
+        <v>WIN</v>
+      </c>
+      <c r="K17" s="10"/>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" s="10" t="s">
+        <v>304</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>283</v>
+      </c>
+      <c r="C18" s="19">
+        <v>46252</v>
+      </c>
+      <c r="D18" s="10" t="s">
+        <v>271</v>
+      </c>
+      <c r="E18" s="10" t="s">
+        <v>285</v>
+      </c>
+      <c r="F18" s="10" t="s">
+        <v>339</v>
+      </c>
+      <c r="G18" s="10" t="str">
+        <f>NURSING2026!$L$13</f>
+        <v>千葉大学</v>
+      </c>
+      <c r="H18" s="10">
+        <f>NURSING2026!$J$14</f>
+        <v>0</v>
+      </c>
+      <c r="I18" s="10">
+        <f>NURSING2026!$L$14</f>
+        <v>4</v>
+      </c>
+      <c r="J18" s="10" t="str">
+        <f>IF(H18&gt;I18,"WIN",IF(H18&lt;I18,"LOSS",""))</f>
+        <v>LOSS</v>
+      </c>
+      <c r="K18" s="10"/>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19" s="10" t="s">
+        <v>328</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>305</v>
+      </c>
+      <c r="C19" s="19">
+        <v>46141</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>305</v>
+      </c>
+      <c r="E19" s="20" t="s">
+        <v>308</v>
+      </c>
+      <c r="F19" s="20" t="s">
+        <v>315</v>
+      </c>
+      <c r="G19" s="10" t="s">
+        <v>314</v>
+      </c>
+      <c r="H19" s="10">
+        <v>2</v>
+      </c>
+      <c r="I19" s="10">
+        <v>4</v>
+      </c>
+      <c r="J19" s="10"/>
+      <c r="K19" s="10" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" s="10" t="s">
+        <v>327</v>
+      </c>
+      <c r="B20" s="10" t="s">
+        <v>305</v>
+      </c>
+      <c r="C20" s="19">
+        <v>46141</v>
+      </c>
+      <c r="D20" s="10" t="s">
+        <v>305</v>
+      </c>
+      <c r="E20" s="20" t="s">
         <v>307</v>
       </c>
-      <c r="B17" s="23" t="s">
-        <v>287</v>
-      </c>
-      <c r="C17" s="24">
-        <v>46251</v>
-      </c>
-      <c r="D17" s="23" t="s">
-        <v>274</v>
-      </c>
-      <c r="E17" s="23" t="s">
-        <v>288</v>
-      </c>
-      <c r="F17" s="23" t="str">
-        <f>'看護部 2026'!$F$13</f>
-        <v>山梨大学</v>
-      </c>
-      <c r="G17" s="23">
-        <f>'看護部 2026'!$D$14</f>
-        <v>3</v>
-      </c>
-      <c r="H17" s="23">
-        <f>'看護部 2026'!$F$14</f>
-        <v>0</v>
-      </c>
-      <c r="I17" s="23" t="str">
-        <f>IF(G17&gt;H17,"WIN",IF(G17&lt;H17,"LOSS",""))</f>
-        <v>WIN</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" t="s">
-        <v>308</v>
-      </c>
-      <c r="B18" s="23" t="s">
-        <v>287</v>
-      </c>
-      <c r="C18" s="24">
-        <v>46252</v>
-      </c>
-      <c r="D18" s="23" t="s">
-        <v>274</v>
-      </c>
-      <c r="E18" s="23" t="s">
-        <v>289</v>
-      </c>
-      <c r="F18" s="23" t="str">
-        <f>'看護部 2026'!$L$13</f>
-        <v>千葉大学</v>
-      </c>
-      <c r="G18" s="23">
-        <f>'看護部 2026'!$J$14</f>
-        <v>0</v>
-      </c>
-      <c r="H18" s="23">
-        <f>'看護部 2026'!$L$14</f>
+      <c r="F20" s="10" t="s">
+        <v>313</v>
+      </c>
+      <c r="G20" s="10" t="s">
+        <v>314</v>
+      </c>
+      <c r="H20" s="10">
+        <v>2</v>
+      </c>
+      <c r="I20" s="10">
         <v>4</v>
       </c>
-      <c r="I18" s="23" t="str">
-        <f>IF(G18&gt;H18,"WIN",IF(G18&lt;H18,"LOSS",""))</f>
-        <v>LOSS</v>
+      <c r="J20" s="10"/>
+      <c r="K20" s="10" t="s">
+        <v>306</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="5"/>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B1048576" xr:uid="{4803B7BF-006D-4D2C-B485-32D63132FB48}">
+      <formula1>"MEN, WOMEN, NURSING, OBOG"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D1048576" xr:uid="{CB68C97B-716C-4205-BF95-E7B073EB72EF}">
+      <formula1>"League, Toitai, Practice, Individual, OBOG"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2273,23 +2702,25 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:12" ht="22.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="23" t="s">
         <v>58</v>
       </c>
-      <c r="C2" s="12"/>
-      <c r="D2" s="12"/>
-      <c r="E2" s="12"/>
-      <c r="F2" s="12"/>
-      <c r="H2" s="12" t="s">
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="H2" s="23" t="s">
         <v>57</v>
       </c>
-      <c r="I2" s="12"/>
-      <c r="J2" s="12"/>
-      <c r="K2" s="12"/>
-      <c r="L2" s="12"/>
+      <c r="I2" s="23"/>
+      <c r="J2" s="23"/>
+      <c r="K2" s="23"/>
+      <c r="L2" s="23"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="B3" s="4"/>
+      <c r="B3" t="s">
+        <v>288</v>
+      </c>
       <c r="C3" s="4"/>
       <c r="D3" s="5" t="s">
         <v>0</v>
@@ -2300,7 +2731,9 @@
       <c r="F3" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="H3" s="6"/>
+      <c r="H3" t="s">
+        <v>289</v>
+      </c>
       <c r="I3" s="6"/>
       <c r="J3" s="5" t="s">
         <v>0</v>
@@ -2313,44 +2746,44 @@
       </c>
     </row>
     <row r="4" spans="2:12" ht="18.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B4" s="15"/>
-      <c r="C4" s="15"/>
-      <c r="D4" s="14">
+      <c r="B4" s="24"/>
+      <c r="C4" s="24"/>
+      <c r="D4" s="25">
         <v>3</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="10">
+      <c r="F4" s="21">
         <v>6</v>
       </c>
-      <c r="H4" s="13"/>
-      <c r="I4" s="13"/>
-      <c r="J4" s="10">
+      <c r="H4" s="26"/>
+      <c r="I4" s="26"/>
+      <c r="J4" s="21">
         <v>6</v>
       </c>
       <c r="K4" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="L4" s="14">
+      <c r="L4" s="25">
         <v>3</v>
       </c>
     </row>
     <row r="5" spans="2:12" ht="18.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B5" s="15"/>
-      <c r="C5" s="15"/>
-      <c r="D5" s="14"/>
+      <c r="B5" s="24"/>
+      <c r="C5" s="24"/>
+      <c r="D5" s="25"/>
       <c r="E5" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F5" s="10"/>
-      <c r="H5" s="13"/>
-      <c r="I5" s="13"/>
-      <c r="J5" s="10"/>
+      <c r="F5" s="21"/>
+      <c r="H5" s="26"/>
+      <c r="I5" s="26"/>
+      <c r="J5" s="21"/>
       <c r="K5" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="L5" s="14"/>
+      <c r="L5" s="25"/>
     </row>
     <row r="6" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B6" s="5" t="s">
@@ -2641,23 +3074,25 @@
       </c>
     </row>
     <row r="16" spans="2:12" ht="22.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="B16" s="12" t="s">
+      <c r="B16" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="C16" s="12"/>
-      <c r="D16" s="12"/>
-      <c r="E16" s="12"/>
-      <c r="F16" s="12"/>
-      <c r="H16" s="12" t="s">
+      <c r="C16" s="23"/>
+      <c r="D16" s="23"/>
+      <c r="E16" s="23"/>
+      <c r="F16" s="23"/>
+      <c r="H16" s="23" t="s">
         <v>103</v>
       </c>
-      <c r="I16" s="12"/>
-      <c r="J16" s="12"/>
-      <c r="K16" s="12"/>
-      <c r="L16" s="12"/>
+      <c r="I16" s="23"/>
+      <c r="J16" s="23"/>
+      <c r="K16" s="23"/>
+      <c r="L16" s="23"/>
     </row>
     <row r="17" spans="2:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="B17" s="6"/>
+      <c r="B17" t="s">
+        <v>290</v>
+      </c>
       <c r="C17" s="6"/>
       <c r="D17" s="5" t="s">
         <v>0</v>
@@ -2668,7 +3103,9 @@
       <c r="F17" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="H17" s="4"/>
+      <c r="H17" t="s">
+        <v>291</v>
+      </c>
       <c r="I17" s="4"/>
       <c r="J17" s="5" t="s">
         <v>0</v>
@@ -2681,44 +3118,44 @@
       </c>
     </row>
     <row r="18" spans="2:12" ht="18.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B18" s="13"/>
-      <c r="C18" s="13"/>
-      <c r="D18" s="14">
+      <c r="B18" s="26"/>
+      <c r="C18" s="26"/>
+      <c r="D18" s="25">
         <v>3</v>
       </c>
       <c r="E18" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="F18" s="10">
+      <c r="F18" s="21">
         <v>5</v>
       </c>
-      <c r="H18" s="13"/>
-      <c r="I18" s="13"/>
-      <c r="J18" s="14">
+      <c r="H18" s="26"/>
+      <c r="I18" s="26"/>
+      <c r="J18" s="25">
         <v>4</v>
       </c>
       <c r="K18" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="L18" s="10">
+      <c r="L18" s="21">
         <v>5</v>
       </c>
     </row>
     <row r="19" spans="2:12" ht="18.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B19" s="13"/>
-      <c r="C19" s="13"/>
-      <c r="D19" s="14"/>
+      <c r="B19" s="26"/>
+      <c r="C19" s="26"/>
+      <c r="D19" s="25"/>
       <c r="E19" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="F19" s="10"/>
-      <c r="H19" s="13"/>
-      <c r="I19" s="13"/>
-      <c r="J19" s="14"/>
+      <c r="F19" s="21"/>
+      <c r="H19" s="26"/>
+      <c r="I19" s="26"/>
+      <c r="J19" s="25"/>
       <c r="K19" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="L19" s="10"/>
+      <c r="L19" s="21"/>
     </row>
     <row r="20" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B20" s="5" t="s">
@@ -3007,23 +3444,25 @@
       </c>
     </row>
     <row r="30" spans="2:12" ht="22.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="B30" s="12" t="s">
+      <c r="B30" s="23" t="s">
         <v>200</v>
       </c>
-      <c r="C30" s="12"/>
-      <c r="D30" s="12"/>
-      <c r="E30" s="12"/>
-      <c r="F30" s="12"/>
-      <c r="H30" s="11" t="s">
+      <c r="C30" s="23"/>
+      <c r="D30" s="23"/>
+      <c r="E30" s="23"/>
+      <c r="F30" s="23"/>
+      <c r="H30" s="22" t="s">
         <v>192</v>
       </c>
-      <c r="I30" s="11"/>
-      <c r="J30" s="11"/>
-      <c r="K30" s="11"/>
-      <c r="L30" s="11"/>
+      <c r="I30" s="22"/>
+      <c r="J30" s="22"/>
+      <c r="K30" s="22"/>
+      <c r="L30" s="22"/>
     </row>
     <row r="31" spans="2:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="B31" s="6"/>
+      <c r="B31" t="s">
+        <v>292</v>
+      </c>
       <c r="C31" s="6"/>
       <c r="D31" s="5" t="s">
         <v>0</v>
@@ -3034,7 +3473,9 @@
       <c r="F31" s="5" t="s">
         <v>180</v>
       </c>
-      <c r="H31" s="6"/>
+      <c r="H31" t="s">
+        <v>293</v>
+      </c>
       <c r="I31" s="6"/>
       <c r="J31" s="5" t="s">
         <v>0</v>
@@ -3047,44 +3488,44 @@
       </c>
     </row>
     <row r="32" spans="2:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="B32" s="13"/>
-      <c r="C32" s="13"/>
-      <c r="D32" s="10">
+      <c r="B32" s="26"/>
+      <c r="C32" s="26"/>
+      <c r="D32" s="21">
         <v>4</v>
       </c>
       <c r="E32" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="F32" s="14">
+      <c r="F32" s="25">
         <v>1</v>
       </c>
-      <c r="H32" s="13"/>
-      <c r="I32" s="13"/>
-      <c r="J32" s="14">
+      <c r="H32" s="26"/>
+      <c r="I32" s="26"/>
+      <c r="J32" s="25">
         <v>2</v>
       </c>
       <c r="K32" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="L32" s="10">
+      <c r="L32" s="21">
         <v>3</v>
       </c>
     </row>
     <row r="33" spans="2:12" ht="18.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B33" s="13"/>
-      <c r="C33" s="13"/>
-      <c r="D33" s="10"/>
+      <c r="B33" s="26"/>
+      <c r="C33" s="26"/>
+      <c r="D33" s="21"/>
       <c r="E33" s="5" t="s">
         <v>181</v>
       </c>
-      <c r="F33" s="14"/>
-      <c r="H33" s="13"/>
-      <c r="I33" s="13"/>
-      <c r="J33" s="14"/>
+      <c r="F33" s="25"/>
+      <c r="H33" s="26"/>
+      <c r="I33" s="26"/>
+      <c r="J33" s="25"/>
       <c r="K33" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="L33" s="10"/>
+      <c r="L33" s="21"/>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B34" s="5" t="s">
@@ -3248,8 +3689,22 @@
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="L18:L19"/>
+    <mergeCell ref="J32:J33"/>
     <mergeCell ref="H32:H33"/>
+    <mergeCell ref="F18:F19"/>
+    <mergeCell ref="H18:H19"/>
+    <mergeCell ref="I18:I19"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="D32:D33"/>
+    <mergeCell ref="F32:F33"/>
+    <mergeCell ref="B32:B33"/>
+    <mergeCell ref="C32:C33"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="D18:D19"/>
+    <mergeCell ref="I32:I33"/>
+    <mergeCell ref="L32:L33"/>
+    <mergeCell ref="H30:L30"/>
     <mergeCell ref="B2:F2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="B4:B5"/>
@@ -3260,24 +3715,10 @@
     <mergeCell ref="I4:I5"/>
     <mergeCell ref="J4:J5"/>
     <mergeCell ref="L4:L5"/>
-    <mergeCell ref="I32:I33"/>
-    <mergeCell ref="J32:J33"/>
-    <mergeCell ref="L32:L33"/>
-    <mergeCell ref="H30:L30"/>
     <mergeCell ref="B16:F16"/>
     <mergeCell ref="H16:L16"/>
-    <mergeCell ref="B32:B33"/>
-    <mergeCell ref="C32:C33"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="D18:D19"/>
-    <mergeCell ref="F18:F19"/>
-    <mergeCell ref="H18:H19"/>
-    <mergeCell ref="I18:I19"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="D32:D33"/>
-    <mergeCell ref="F32:F33"/>
     <mergeCell ref="J18:J19"/>
+    <mergeCell ref="L18:L19"/>
   </mergeCells>
   <phoneticPr fontId="5"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3301,23 +3742,25 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="22" t="s">
         <v>122</v>
       </c>
-      <c r="C2" s="11"/>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
-      <c r="F2" s="11"/>
-      <c r="H2" s="11" t="s">
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="H2" s="22" t="s">
         <v>136</v>
       </c>
-      <c r="I2" s="11"/>
-      <c r="J2" s="11"/>
-      <c r="K2" s="11"/>
-      <c r="L2" s="11"/>
+      <c r="I2" s="22"/>
+      <c r="J2" s="22"/>
+      <c r="K2" s="22"/>
+      <c r="L2" s="22"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="B3" s="6"/>
+      <c r="B3" t="s">
+        <v>294</v>
+      </c>
       <c r="C3" s="6"/>
       <c r="D3" s="5" t="s">
         <v>0</v>
@@ -3328,7 +3771,9 @@
       <c r="F3" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="H3" s="6"/>
+      <c r="H3" t="s">
+        <v>296</v>
+      </c>
       <c r="I3" s="6"/>
       <c r="J3" s="5" t="s">
         <v>0</v>
@@ -3341,44 +3786,44 @@
       </c>
     </row>
     <row r="4" spans="2:12" ht="18.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B4" s="13"/>
-      <c r="C4" s="13"/>
-      <c r="D4" s="14">
+      <c r="B4" s="26"/>
+      <c r="C4" s="26"/>
+      <c r="D4" s="25">
         <v>1</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="F4" s="10">
+      <c r="F4" s="21">
         <v>4</v>
       </c>
-      <c r="H4" s="13"/>
-      <c r="I4" s="13"/>
-      <c r="J4" s="14">
+      <c r="H4" s="26"/>
+      <c r="I4" s="26"/>
+      <c r="J4" s="25">
         <v>0</v>
       </c>
       <c r="K4" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="L4" s="10">
+      <c r="L4" s="21">
         <v>5</v>
       </c>
     </row>
     <row r="5" spans="2:12" ht="18.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B5" s="13"/>
-      <c r="C5" s="13"/>
-      <c r="D5" s="14"/>
+      <c r="B5" s="26"/>
+      <c r="C5" s="26"/>
+      <c r="D5" s="25"/>
       <c r="E5" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="F5" s="10"/>
-      <c r="H5" s="13"/>
-      <c r="I5" s="13"/>
-      <c r="J5" s="14"/>
+      <c r="F5" s="21"/>
+      <c r="H5" s="26"/>
+      <c r="I5" s="26"/>
+      <c r="J5" s="25"/>
       <c r="K5" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="L5" s="10"/>
+      <c r="L5" s="21"/>
     </row>
     <row r="6" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B6" s="5" t="s">
@@ -3553,23 +3998,25 @@
       <c r="L11" s="1"/>
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="B12" s="20" t="s">
+      <c r="B12" s="27" t="s">
         <v>148</v>
       </c>
-      <c r="C12" s="20"/>
-      <c r="D12" s="20"/>
-      <c r="E12" s="20"/>
-      <c r="F12" s="20"/>
-      <c r="H12" s="20" t="s">
+      <c r="C12" s="27"/>
+      <c r="D12" s="27"/>
+      <c r="E12" s="27"/>
+      <c r="F12" s="27"/>
+      <c r="H12" s="27" t="s">
         <v>155</v>
       </c>
-      <c r="I12" s="20"/>
-      <c r="J12" s="20"/>
-      <c r="K12" s="20"/>
-      <c r="L12" s="20"/>
+      <c r="I12" s="27"/>
+      <c r="J12" s="27"/>
+      <c r="K12" s="27"/>
+      <c r="L12" s="27"/>
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="B13" s="6"/>
+      <c r="B13" t="s">
+        <v>295</v>
+      </c>
       <c r="C13" s="6"/>
       <c r="D13" s="5" t="s">
         <v>0</v>
@@ -3580,7 +4027,9 @@
       <c r="F13" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="H13" s="4"/>
+      <c r="H13" t="s">
+        <v>297</v>
+      </c>
       <c r="I13" s="4"/>
       <c r="J13" s="5" t="s">
         <v>0</v>
@@ -3593,44 +4042,44 @@
       </c>
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="B14" s="13"/>
-      <c r="C14" s="13"/>
-      <c r="D14" s="10">
+      <c r="B14" s="26"/>
+      <c r="C14" s="26"/>
+      <c r="D14" s="21">
         <v>3</v>
       </c>
       <c r="E14" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="F14" s="14">
+      <c r="F14" s="25">
         <v>2</v>
       </c>
-      <c r="H14" s="15"/>
-      <c r="I14" s="15"/>
-      <c r="J14" s="14">
+      <c r="H14" s="24"/>
+      <c r="I14" s="24"/>
+      <c r="J14" s="25">
         <v>0</v>
       </c>
       <c r="K14" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="L14" s="21">
+      <c r="L14" s="28">
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="B15" s="13"/>
-      <c r="C15" s="13"/>
-      <c r="D15" s="10"/>
+      <c r="B15" s="26"/>
+      <c r="C15" s="26"/>
+      <c r="D15" s="21"/>
       <c r="E15" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="F15" s="14"/>
-      <c r="H15" s="15"/>
-      <c r="I15" s="15"/>
-      <c r="J15" s="14"/>
+      <c r="F15" s="25"/>
+      <c r="H15" s="24"/>
+      <c r="I15" s="24"/>
+      <c r="J15" s="25"/>
       <c r="K15" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="L15" s="21"/>
+      <c r="L15" s="28"/>
     </row>
     <row r="16" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B16" s="5" t="s">
@@ -3795,23 +4244,25 @@
       <c r="L21" s="1"/>
     </row>
     <row r="22" spans="2:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="B22" s="11" t="s">
+      <c r="B22" s="22" t="s">
         <v>163</v>
       </c>
-      <c r="C22" s="11"/>
-      <c r="D22" s="11"/>
-      <c r="E22" s="11"/>
-      <c r="F22" s="11"/>
-      <c r="H22" s="11" t="s">
+      <c r="C22" s="22"/>
+      <c r="D22" s="22"/>
+      <c r="E22" s="22"/>
+      <c r="F22" s="22"/>
+      <c r="H22" s="22" t="s">
         <v>164</v>
       </c>
-      <c r="I22" s="11"/>
-      <c r="J22" s="11"/>
-      <c r="K22" s="11"/>
-      <c r="L22" s="11"/>
+      <c r="I22" s="22"/>
+      <c r="J22" s="22"/>
+      <c r="K22" s="22"/>
+      <c r="L22" s="22"/>
     </row>
     <row r="23" spans="2:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="B23" s="6"/>
+      <c r="B23" t="s">
+        <v>298</v>
+      </c>
       <c r="C23" s="6"/>
       <c r="D23" s="5" t="s">
         <v>0</v>
@@ -3822,7 +4273,9 @@
       <c r="F23" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="H23" s="6"/>
+      <c r="H23" t="s">
+        <v>299</v>
+      </c>
       <c r="I23" s="6"/>
       <c r="J23" s="5" t="s">
         <v>0</v>
@@ -3831,48 +4284,48 @@
         <v>1</v>
       </c>
       <c r="L23" s="5" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
     </row>
     <row r="24" spans="2:12" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B24" s="13"/>
-      <c r="C24" s="13"/>
-      <c r="D24" s="10">
+      <c r="B24" s="26"/>
+      <c r="C24" s="26"/>
+      <c r="D24" s="21">
         <v>2</v>
       </c>
       <c r="E24" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="F24" s="14">
+      <c r="F24" s="25">
         <v>1</v>
       </c>
       <c r="H24" s="6"/>
       <c r="I24" s="6"/>
-      <c r="J24" s="16">
+      <c r="J24" s="29">
         <v>2</v>
       </c>
       <c r="K24" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="L24" s="18">
+      <c r="L24" s="31">
         <v>1</v>
       </c>
     </row>
     <row r="25" spans="2:12" ht="18.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B25" s="13"/>
-      <c r="C25" s="13"/>
-      <c r="D25" s="10"/>
+      <c r="B25" s="26"/>
+      <c r="C25" s="26"/>
+      <c r="D25" s="21"/>
       <c r="E25" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="F25" s="14"/>
+      <c r="F25" s="25"/>
       <c r="H25" s="6"/>
       <c r="I25" s="6"/>
-      <c r="J25" s="17"/>
+      <c r="J25" s="30"/>
       <c r="K25" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="L25" s="19"/>
+      <c r="L25" s="32"/>
     </row>
     <row r="26" spans="2:12" ht="18.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B26" s="5" t="s">
@@ -3975,16 +4428,18 @@
       <c r="E29" s="3"/>
     </row>
     <row r="30" spans="2:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="B30" s="11" t="s">
+      <c r="B30" s="22" t="s">
         <v>170</v>
       </c>
-      <c r="C30" s="11"/>
-      <c r="D30" s="11"/>
-      <c r="E30" s="11"/>
-      <c r="F30" s="11"/>
+      <c r="C30" s="22"/>
+      <c r="D30" s="22"/>
+      <c r="E30" s="22"/>
+      <c r="F30" s="22"/>
     </row>
     <row r="31" spans="2:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="B31" s="4"/>
+      <c r="B31" t="s">
+        <v>300</v>
+      </c>
       <c r="C31" s="6"/>
       <c r="D31" s="5" t="s">
         <v>0</v>
@@ -3997,26 +4452,26 @@
       </c>
     </row>
     <row r="32" spans="2:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="B32" s="15"/>
-      <c r="C32" s="13"/>
-      <c r="D32" s="14">
+      <c r="B32" s="24"/>
+      <c r="C32" s="26"/>
+      <c r="D32" s="25">
         <v>0</v>
       </c>
       <c r="E32" s="5" t="s">
         <v>172</v>
       </c>
-      <c r="F32" s="10">
+      <c r="F32" s="21">
         <v>3</v>
       </c>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="B33" s="15"/>
-      <c r="C33" s="13"/>
-      <c r="D33" s="14"/>
+      <c r="B33" s="24"/>
+      <c r="C33" s="26"/>
+      <c r="D33" s="25"/>
       <c r="E33" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="F33" s="10"/>
+      <c r="F33" s="21"/>
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.55000000000000004">
       <c r="B34" s="5" t="s">
@@ -4071,16 +4526,13 @@
     </row>
   </sheetData>
   <mergeCells count="33">
-    <mergeCell ref="B2:F2"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="H4:H5"/>
-    <mergeCell ref="I4:I5"/>
-    <mergeCell ref="J4:J5"/>
-    <mergeCell ref="L4:L5"/>
+    <mergeCell ref="J24:J25"/>
+    <mergeCell ref="L24:L25"/>
+    <mergeCell ref="B32:B33"/>
+    <mergeCell ref="C32:C33"/>
+    <mergeCell ref="D32:D33"/>
+    <mergeCell ref="F32:F33"/>
+    <mergeCell ref="B30:F30"/>
     <mergeCell ref="H12:L12"/>
     <mergeCell ref="B24:B25"/>
     <mergeCell ref="C24:C25"/>
@@ -4097,13 +4549,16 @@
     <mergeCell ref="L14:L15"/>
     <mergeCell ref="H22:L22"/>
     <mergeCell ref="D24:D25"/>
-    <mergeCell ref="J24:J25"/>
-    <mergeCell ref="L24:L25"/>
-    <mergeCell ref="B32:B33"/>
-    <mergeCell ref="C32:C33"/>
-    <mergeCell ref="D32:D33"/>
-    <mergeCell ref="F32:F33"/>
-    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="H4:H5"/>
+    <mergeCell ref="I4:I5"/>
+    <mergeCell ref="J4:J5"/>
+    <mergeCell ref="L4:L5"/>
   </mergeCells>
   <phoneticPr fontId="5"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4139,23 +4594,25 @@
       <c r="L1" s="1"/>
     </row>
     <row r="2" spans="2:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="22" t="s">
         <v>201</v>
       </c>
-      <c r="C2" s="11"/>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
-      <c r="F2" s="11"/>
-      <c r="H2" s="11" t="s">
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="H2" s="22" t="s">
         <v>215</v>
       </c>
-      <c r="I2" s="11"/>
-      <c r="J2" s="11"/>
-      <c r="K2" s="11"/>
-      <c r="L2" s="11"/>
+      <c r="I2" s="22"/>
+      <c r="J2" s="22"/>
+      <c r="K2" s="22"/>
+      <c r="L2" s="22"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="B3" s="6"/>
+      <c r="B3" t="s">
+        <v>301</v>
+      </c>
       <c r="C3" s="6"/>
       <c r="D3" s="5" t="s">
         <v>0</v>
@@ -4166,7 +4623,9 @@
       <c r="F3" s="5" t="s">
         <v>202</v>
       </c>
-      <c r="H3" s="4"/>
+      <c r="H3" t="s">
+        <v>302</v>
+      </c>
       <c r="I3" s="6"/>
       <c r="J3" s="5" t="s">
         <v>0</v>
@@ -4179,44 +4638,44 @@
       </c>
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="B4" s="13"/>
-      <c r="C4" s="13"/>
-      <c r="D4" s="10">
+      <c r="B4" s="26"/>
+      <c r="C4" s="26"/>
+      <c r="D4" s="21">
         <v>4</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="F4" s="14">
+      <c r="F4" s="25">
         <v>1</v>
       </c>
-      <c r="H4" s="15"/>
-      <c r="I4" s="13"/>
-      <c r="J4" s="10">
+      <c r="H4" s="24"/>
+      <c r="I4" s="26"/>
+      <c r="J4" s="21">
         <v>3</v>
       </c>
       <c r="K4" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="L4" s="14">
+      <c r="L4" s="25">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="2:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="B5" s="13"/>
-      <c r="C5" s="13"/>
-      <c r="D5" s="10"/>
+      <c r="B5" s="26"/>
+      <c r="C5" s="26"/>
+      <c r="D5" s="21"/>
       <c r="E5" s="5" t="s">
         <v>181</v>
       </c>
-      <c r="F5" s="14"/>
-      <c r="H5" s="15"/>
-      <c r="I5" s="13"/>
-      <c r="J5" s="10"/>
+      <c r="F5" s="25"/>
+      <c r="H5" s="24"/>
+      <c r="I5" s="26"/>
+      <c r="J5" s="21"/>
       <c r="K5" s="5" t="s">
         <v>216</v>
       </c>
-      <c r="L5" s="14"/>
+      <c r="L5" s="25"/>
     </row>
     <row r="6" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B6" s="5" t="s">
@@ -4377,23 +4836,25 @@
       </c>
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="B12" s="11" t="s">
+      <c r="B12" s="22" t="s">
         <v>225</v>
       </c>
-      <c r="C12" s="11"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11"/>
-      <c r="H12" s="11" t="s">
+      <c r="C12" s="22"/>
+      <c r="D12" s="22"/>
+      <c r="E12" s="22"/>
+      <c r="F12" s="22"/>
+      <c r="H12" s="22" t="s">
         <v>235</v>
       </c>
-      <c r="I12" s="11"/>
-      <c r="J12" s="11"/>
-      <c r="K12" s="11"/>
-      <c r="L12" s="11"/>
+      <c r="I12" s="22"/>
+      <c r="J12" s="22"/>
+      <c r="K12" s="22"/>
+      <c r="L12" s="22"/>
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="B13" s="6"/>
+      <c r="B13" t="s">
+        <v>303</v>
+      </c>
       <c r="C13" s="6"/>
       <c r="D13" s="5" t="s">
         <v>0</v>
@@ -4404,7 +4865,9 @@
       <c r="F13" s="5" t="s">
         <v>202</v>
       </c>
-      <c r="H13" s="6"/>
+      <c r="H13" t="s">
+        <v>304</v>
+      </c>
       <c r="I13" s="6"/>
       <c r="J13" s="5" t="s">
         <v>0</v>
@@ -4417,44 +4880,44 @@
       </c>
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="B14" s="13"/>
-      <c r="C14" s="13"/>
-      <c r="D14" s="10">
+      <c r="B14" s="26"/>
+      <c r="C14" s="26"/>
+      <c r="D14" s="21">
         <v>3</v>
       </c>
       <c r="E14" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="F14" s="14">
+      <c r="F14" s="25">
         <v>0</v>
       </c>
-      <c r="H14" s="13"/>
-      <c r="I14" s="13"/>
-      <c r="J14" s="14">
+      <c r="H14" s="26"/>
+      <c r="I14" s="26"/>
+      <c r="J14" s="25">
         <v>0</v>
       </c>
       <c r="K14" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="L14" s="10">
+      <c r="L14" s="21">
         <v>4</v>
       </c>
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="B15" s="13"/>
-      <c r="C15" s="13"/>
-      <c r="D15" s="10"/>
+      <c r="B15" s="26"/>
+      <c r="C15" s="26"/>
+      <c r="D15" s="21"/>
       <c r="E15" s="5" t="s">
         <v>226</v>
       </c>
-      <c r="F15" s="14"/>
-      <c r="H15" s="13"/>
-      <c r="I15" s="13"/>
-      <c r="J15" s="14"/>
+      <c r="F15" s="25"/>
+      <c r="H15" s="26"/>
+      <c r="I15" s="26"/>
+      <c r="J15" s="25"/>
       <c r="K15" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="L15" s="10"/>
+      <c r="L15" s="21"/>
     </row>
     <row r="16" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B16" s="5" t="s">
@@ -4612,6 +5075,16 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="H4:H5"/>
+    <mergeCell ref="I4:I5"/>
+    <mergeCell ref="J4:J5"/>
+    <mergeCell ref="L4:L5"/>
+    <mergeCell ref="B2:F2"/>
     <mergeCell ref="B12:F12"/>
     <mergeCell ref="H12:L12"/>
     <mergeCell ref="B14:B15"/>
@@ -4622,19 +5095,254 @@
     <mergeCell ref="I14:I15"/>
     <mergeCell ref="J14:J15"/>
     <mergeCell ref="L14:L15"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="H4:H5"/>
-    <mergeCell ref="I4:I5"/>
-    <mergeCell ref="J4:J5"/>
-    <mergeCell ref="L4:L5"/>
-    <mergeCell ref="B2:F2"/>
   </mergeCells>
   <phoneticPr fontId="5"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="56" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B650AD4B-55E1-46CB-ABA1-3C715F61555B}">
+  <dimension ref="A1:M13"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="6" max="6" width="14.25" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.25" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.58203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="B1" t="s">
+        <v>329</v>
+      </c>
+      <c r="F1" t="s">
+        <v>329</v>
+      </c>
+      <c r="J1" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="B2" s="10"/>
+      <c r="C2" s="33" t="s">
+        <v>317</v>
+      </c>
+      <c r="D2" s="34"/>
+      <c r="E2" s="35"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="33" t="s">
+        <v>319</v>
+      </c>
+      <c r="H2" s="34"/>
+      <c r="I2" s="35"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="33" t="s">
+        <v>320</v>
+      </c>
+      <c r="L2" s="34"/>
+      <c r="M2" s="35"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="B3" s="10"/>
+      <c r="C3" s="11" t="s">
+        <v>318</v>
+      </c>
+      <c r="D3" s="10"/>
+      <c r="E3" s="12" t="s">
+        <v>311</v>
+      </c>
+      <c r="F3" s="10"/>
+      <c r="G3" s="11" t="s">
+        <v>318</v>
+      </c>
+      <c r="H3" s="10"/>
+      <c r="I3" s="12" t="s">
+        <v>311</v>
+      </c>
+      <c r="J3" s="10"/>
+      <c r="K3" s="11" t="s">
+        <v>318</v>
+      </c>
+      <c r="L3" s="10"/>
+      <c r="M3" s="12" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" s="10" t="s">
+        <v>321</v>
+      </c>
+      <c r="C4" s="11"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="11"/>
+      <c r="H4" s="10"/>
+      <c r="I4" s="12"/>
+      <c r="J4" s="10"/>
+      <c r="K4" s="11"/>
+      <c r="L4" s="10"/>
+      <c r="M4" s="12"/>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="10" t="s">
+        <v>322</v>
+      </c>
+      <c r="C5" s="11"/>
+      <c r="D5" s="10"/>
+      <c r="E5" s="12"/>
+      <c r="F5" t="s">
+        <v>328</v>
+      </c>
+      <c r="G5" s="11" t="s">
+        <v>315</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>326</v>
+      </c>
+      <c r="I5" s="12" t="s">
+        <v>314</v>
+      </c>
+      <c r="J5" s="10"/>
+      <c r="K5" s="11"/>
+      <c r="L5" s="10"/>
+      <c r="M5" s="12"/>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="10" t="s">
+        <v>323</v>
+      </c>
+      <c r="C6" s="11"/>
+      <c r="D6" s="10"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="10"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="10"/>
+      <c r="I6" s="12"/>
+      <c r="J6" t="s">
+        <v>327</v>
+      </c>
+      <c r="K6" s="11" t="s">
+        <v>325</v>
+      </c>
+      <c r="L6" s="16" t="s">
+        <v>326</v>
+      </c>
+      <c r="M6" s="12" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="10" t="s">
+        <v>324</v>
+      </c>
+      <c r="C7" s="11"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="12"/>
+      <c r="F7" s="10"/>
+      <c r="G7" s="11"/>
+      <c r="H7" s="10"/>
+      <c r="I7" s="12"/>
+      <c r="J7" s="10"/>
+      <c r="K7" s="11"/>
+      <c r="L7" s="10"/>
+      <c r="M7" s="12"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="B8" s="10"/>
+      <c r="C8" s="13"/>
+      <c r="D8" s="14"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="10"/>
+      <c r="G8" s="13"/>
+      <c r="H8" s="14"/>
+      <c r="I8" s="15"/>
+      <c r="J8" s="10"/>
+      <c r="K8" s="13"/>
+      <c r="L8" s="14"/>
+      <c r="M8" s="15"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="B9" s="10"/>
+      <c r="C9" s="10"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="10"/>
+      <c r="F9" s="10"/>
+      <c r="G9" s="10"/>
+      <c r="H9" s="10"/>
+      <c r="I9" s="10"/>
+      <c r="J9" s="10"/>
+      <c r="K9" s="10"/>
+      <c r="L9" s="10"/>
+      <c r="M9" s="10"/>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="B10" s="10"/>
+      <c r="C10" s="10"/>
+      <c r="D10" s="10"/>
+      <c r="E10" s="10"/>
+      <c r="F10" s="10"/>
+      <c r="G10" s="10"/>
+      <c r="H10" s="10"/>
+      <c r="I10" s="10"/>
+      <c r="J10" s="10"/>
+      <c r="K10" s="10"/>
+      <c r="L10" s="10"/>
+      <c r="M10" s="10"/>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="B11" s="10"/>
+      <c r="C11" s="10"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="10"/>
+      <c r="F11" s="10"/>
+      <c r="G11" s="10"/>
+      <c r="H11" s="10"/>
+      <c r="I11" s="10"/>
+      <c r="J11" s="10"/>
+      <c r="K11" s="10"/>
+      <c r="L11" s="10"/>
+      <c r="M11" s="10"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="B12" s="10"/>
+      <c r="C12" s="10"/>
+      <c r="D12" s="10"/>
+      <c r="E12" s="10"/>
+      <c r="F12" s="10"/>
+      <c r="G12" s="10"/>
+      <c r="H12" s="10"/>
+      <c r="I12" s="10"/>
+      <c r="J12" s="10"/>
+      <c r="K12" s="10"/>
+      <c r="L12" s="10"/>
+      <c r="M12" s="10"/>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="B13" s="10"/>
+      <c r="C13" s="10"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="10"/>
+      <c r="F13" s="10"/>
+      <c r="G13" s="10"/>
+      <c r="H13" s="10"/>
+      <c r="I13" s="10"/>
+      <c r="J13" s="10"/>
+      <c r="K13" s="10"/>
+      <c r="L13" s="10"/>
+      <c r="M13" s="10"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="G2:I2"/>
+    <mergeCell ref="K2:M2"/>
+  </mergeCells>
+  <phoneticPr fontId="5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>